--- a/工作一对比结果/cnn-dir0.5baseline.xlsx
+++ b/工作一对比结果/cnn-dir0.5baseline.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,10 +510,10 @@
         <v>53.24</v>
       </c>
       <c r="I2" t="n">
-        <v>91.69</v>
+        <v>55.05</v>
       </c>
       <c r="J2" t="n">
-        <v>86.87</v>
+        <v>85.09</v>
       </c>
     </row>
     <row r="3">
@@ -546,10 +546,10 @@
         <v>41.17</v>
       </c>
       <c r="I3" t="n">
-        <v>91.69</v>
+        <v>54.89</v>
       </c>
       <c r="J3" t="n">
-        <v>88.09</v>
+        <v>86.52</v>
       </c>
     </row>
     <row r="4">
@@ -582,10 +582,10 @@
         <v>33.92</v>
       </c>
       <c r="I4" t="n">
-        <v>91.81</v>
+        <v>54.97</v>
       </c>
       <c r="J4" t="n">
-        <v>88.31</v>
+        <v>86.89</v>
       </c>
     </row>
     <row r="5">
@@ -618,10 +618,46 @@
         <v>28.74</v>
       </c>
       <c r="I5" t="n">
-        <v>92.41</v>
+        <v>54.95</v>
       </c>
       <c r="J5" t="n">
-        <v>88.98999999999999</v>
+        <v>87.76000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>nonIID(0.5)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FedAGSA</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>37</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="E6" t="n">
+        <v>87</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="G6" t="n">
+        <v>191</v>
+      </c>
+      <c r="H6" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25.24</v>
+      </c>
+      <c r="J6" t="n">
+        <v>86.51000000000001</v>
       </c>
     </row>
   </sheetData>
